--- a/output/xlsx/matriz_requerimientos.xlsx
+++ b/output/xlsx/matriz_requerimientos.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trazabilidad Requerimientos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trazabilidad Requerimientos'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trazabilidad Requerimientos'!$A$1:$G$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -418,16 +418,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="47" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1577,8 +1577,1932 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RF-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Registrar ejemplar físico asociado a libro y sucursal</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir registrar un ejemplar asociándolo a un libro y sucursal existentes, asignando automáticamente el estado inicial "disponible" y registrando su condición física.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RF-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Generar automáticamente código de identificación del ejemplar</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá generar automáticamente el código de identificación del ejemplar con el formato bib-{sucursal}-{categoría}-{secuencial}.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>RF-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Dar de baja un ejemplar registrando el motivo</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir dar de baja un ejemplar registrando el motivo correspondiente.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>RF-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Impedir dar de baja un ejemplar prestado o dado de baja</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá impedir dar de baja un ejemplar que se encuentre actualmente prestado o ya dado de baja.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RF-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Consultar ejemplares asociados a un libro específico</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir consultar los ejemplares asociados a un libro específico con su estado actual.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>RF-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>El libro y la sucursal deben existir previamente en el sistema</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el libro y la sucursal deben existir previamente en el sistema.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RF-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>El código de ejemplar debe ser único en todo el sistema</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el código de ejemplar debe ser único en todo el sistema.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>RF-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>El secuencial del código se genera automáticamente por sucursal y categoría</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el secuencial del código se genera automáticamente por sucursal y categoría.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RF-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Buscar libros por término, categoría o sucursal</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir buscar libros por título, autor o isbn utilizando un término de búsqueda.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>RF-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Filtrar resultados por categoría y sucursal</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir filtrar los resultados por categoría del libro y por sucursal con ejemplares disponibles.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RF-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mostrar cantidad de ejemplares disponibles</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar la cantidad de ejemplares disponibles de cada libro en los resultados de búsqueda.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>RF-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Paginar resultados de búsqueda</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá paginar los resultados de búsqueda cuando excedan 20 registros.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RF-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Consultar disponibilidad detallada por sucursal</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir consultar la disponibilidad detallada de un libro mostrando por cada sucursal el total de ejemplares y la cantidad disponible.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>RF-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Los resultados deben mostrar únicamente libros activos con al menos un ejemplar registrado</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá los resultados deben mostrar únicamente libros activos con al menos un ejemplar registrado.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RNF-001</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Disponibilidad de información en tiempo real</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la consulta de disponibilidad debe reflejar el estado actual de los ejemplares en tiempo real.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>No funcional</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>RF-045</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>La búsqueda utiliza coincidencia parcial para permitir resultados aproximados</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la búsqueda utiliza coincidencia parcial para permitir resultados aproximados.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>RNF-002</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Disponibilidad de información en tiempo real</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la búsqueda utiliza coincidencia parcial (ilike) para permitir resultados aproximados. La disponibilidad se calcula en tiempo real consultando el estado actual de los ejemplares.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>No funcional</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>RF-046</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Registrar un libro con metadatos bibliográficos</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir registrar un libro con título, autor, isbn, editorial, año de publicación y categoría.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>RF-047</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Validar unicidad y formato de isbn</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá validar que el isbn sea único en el sistema y tenga un formato correcto (isbn-10 o isbn-13).</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>RF-048</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Modificar la información bibliográfica de un libro existente</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir modificar la información bibliográfica de un libro existente.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>RF-049</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Consultar libros aplicando filtros por título, autor y categoría</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir consultar libros aplicando filtros por título, autor y categoría.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>RF-050</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Mostrar la cantidad de ejemplares asociados al consultar un libro</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar la cantidad de ejemplares asociados al consultar un libro.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RF-051</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Paginar los resultados de la consulta cuando existan más de 20 libros</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá paginar los resultados de la consulta cuando existan más de 20 libros.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>RF-052</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>La categoría del libro debe pertenecer al conjunto predefinido del sistema</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la categoría del libro debe pertenecer al conjunto predefinido del sistema.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>RF-053</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>El libro debe estar registrado antes de poder crear ejemplares físicos asociados</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el libro debe estar registrado antes de poder crear ejemplares físicos asociados.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>HU-001 – HU-001 - Gestión de libros</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>RF-054</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Registrar préstamo de ejemplar disponible</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir registrar un préstamo seleccionando un ejemplar disponible y un lector.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>RF-055</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Verificar estado disponible del ejemplar</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá verificar que el ejemplar se encuentre en estado disponible antes de registrar el préstamo.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>RF-056</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Verificar que el lector esté activo</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá verificar que el lector esté activo en el sistema.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>RNF-003</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Verificar límite máximo de préstamos activos</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá verificar que el lector no haya alcanzado el límite máximo de préstamos activos simultáneos.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>No funcional</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>RF-057</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Impedir préstamo con préstamos vencidos</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá impedir el préstamo cuando el lector tenga préstamos vencidos sin devolver.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>RF-058</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Calcular fecha de devolución esperada</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá calcular automáticamente la fecha de devolución esperada según los días configurados.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>RF-059</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Cambiar estado del ejemplar a prestado</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá cambiar el estado del ejemplar a "prestado" inmediatamente después de registrar el préstamo.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>RF-060</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Registrar bibliotecario operador</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá registrar el bibliotecario que realizó la operación.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>RF-061</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Solo los bibliotecarios y administradores pueden registrar préstamos</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá solo los bibliotecarios y administradores pueden registrar préstamos.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>RF-062</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Un lector puede tener como máximo 3 préstamos activos simultáneamente</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá un lector puede tener como máximo 3 préstamos activos simultáneamente.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>RNF-004</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>El plazo máximo de préstamo es de 15 días</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el plazo máximo de préstamo es de 15 días.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>No funcional</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>RF-063</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>No se permiten préstamos a lectores con devoluciones pendientes vencidas</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá no se permiten préstamos a lectores con devoluciones pendientes vencidas.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>RF-064</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>El identificador del lector se obtiene del sistema, no de un dato proporcionado por el cliente. El préstamo debe quedar asociado al bibliotecario que realizó la operación para trazabilidad. La disponibilidad del ejemplar debe verificarse inmediatamente antes de registrar el préstamo</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el identificador del lector se obtiene del sistema, no de un dato proporcionado por el cliente. El préstamo debe quedar asociado al bibliotecario que realizó la operación para trazabilidad. La disponibilidad del ejemplar debe verificarse inmediatamente antes de registrar el préstamo.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>RF-065</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Registrar la devolución de un ejemplar</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir registrar la devolución de un ejemplar prestado.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>RF-066</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Verificar existencia de préstamo activo</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá verificar que exista un préstamo activo relacionado con el ejemplar.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>RF-067</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Actualizar información del préstamo después de la devolución</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>RF-068</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Mostrar mensaje de confirmación de devolución</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>RF-069</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Permitir continuar con el proceso cuando los datos sean correctos</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>RF-070</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>La devolución debe corresponder a un préstamo registrado</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>RF-071</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>HU-005 – HU-005 - Devolución de ejemplares</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>RF-072</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Solicitar transferencia de ejemplar disponible</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir solicitar la transferencia de un ejemplar disponible.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>RF-073</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Verificar disponibilidad del ejemplar</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá verificar que el ejemplar se encuentre disponible.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>RF-074</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Registrar sucursal de origen y destino</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá registrar la sucursal de origen y la sucursal de destino.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pendiente de definición y validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>RF-075</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Permitir continuar con el proceso cuando los datos sean correctos</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>RF-076</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>El ejemplar debe estar disponible</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá el ejemplar debe estar disponible.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>RF-077</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Las sucursales de origen y destino deben ser diferentes</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá las sucursales de origen y destino deben ser diferentes.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>RF-078</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>El sistema deberá todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Pendiente de validación</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G31"/>
+  <autoFilter ref="A1:G83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>